--- a/eval/results/evaluation_metrics_by_qid_new30.xlsx
+++ b/eval/results/evaluation_metrics_by_qid_new30.xlsx
@@ -501,25 +501,25 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9056603773584906</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -548,19 +548,19 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
@@ -569,7 +569,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -642,19 +642,19 @@
         <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="D5" t="n">
-        <v>0.875</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.823529411764706</v>
+        <v>0.8679245283018867</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -689,19 +689,19 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -710,7 +710,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -833,25 +833,25 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -880,25 +880,25 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1253,19 +1253,19 @@
         <v>30</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>27</v>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1303,25 +1303,25 @@
         <v>0.7</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1676,7 +1676,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1691,10 +1691,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1738,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -2193,7 +2193,7 @@
         <v>30</v>
       </c>
       <c r="B38" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2208,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
         <v>19</v>
@@ -2240,7 +2240,7 @@
         <v>30</v>
       </c>
       <c r="B39" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -2255,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
         <v>19</v>
@@ -2334,7 +2334,7 @@
         <v>30</v>
       </c>
       <c r="B41" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -2349,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
@@ -2522,7 +2522,7 @@
         <v>30</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
         <v>19</v>
@@ -2569,7 +2569,7 @@
         <v>30</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -2584,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
         <v>6</v>
-      </c>
-      <c r="H46" t="n">
-        <v>5</v>
       </c>
       <c r="I46" t="n">
         <v>19</v>
@@ -2616,7 +2616,7 @@
         <v>30</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>24</v>
@@ -2663,7 +2663,7 @@
         <v>30</v>
       </c>
       <c r="B48" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>24</v>
@@ -2992,7 +2992,7 @@
         <v>30</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
         <v>24</v>
@@ -3086,7 +3086,7 @@
         <v>30</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -3101,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
         <v>4</v>
-      </c>
-      <c r="H57" t="n">
-        <v>5</v>
       </c>
       <c r="I57" t="n">
         <v>21</v>
@@ -3462,28 +3462,28 @@
         <v>30</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C65" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>23</v>
+      </c>
+      <c r="H65" t="n">
         <v>1</v>
       </c>
-      <c r="D65" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F65" t="n">
-        <v>4</v>
-      </c>
-      <c r="G65" t="n">
-        <v>24</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3509,19 +3509,19 @@
         <v>30</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E66" t="n">
         <v>0.5</v>
       </c>
-      <c r="E66" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
         <v>24</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3791,19 +3791,19 @@
         <v>30</v>
       </c>
       <c r="B72" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>24</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3838,19 +3838,19 @@
         <v>30</v>
       </c>
       <c r="B73" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
         <v>23</v>
@@ -3859,7 +3859,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>30</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -3900,10 +3900,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I74" t="n">
         <v>7</v>
@@ -3932,7 +3932,7 @@
         <v>30</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H75" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I75" t="n">
         <v>7</v>
@@ -4073,7 +4073,7 @@
         <v>30</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -4088,10 +4088,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I78" t="n">
         <v>7</v>
@@ -4214,7 +4214,7 @@
         <v>30</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -4229,10 +4229,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
+        <v>12</v>
+      </c>
+      <c r="H81" t="n">
         <v>11</v>
-      </c>
-      <c r="H81" t="n">
-        <v>12</v>
       </c>
       <c r="I81" t="n">
         <v>7</v>
@@ -4261,7 +4261,7 @@
         <v>30</v>
       </c>
       <c r="B82" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -4276,10 +4276,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H82" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I82" t="n">
         <v>7</v>
@@ -4355,7 +4355,7 @@
         <v>30</v>
       </c>
       <c r="B84" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -4370,10 +4370,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I84" t="n">
         <v>19</v>
@@ -4496,7 +4496,7 @@
         <v>30</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -4511,10 +4511,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I87" t="n">
         <v>19</v>
@@ -4684,7 +4684,7 @@
         <v>30</v>
       </c>
       <c r="B91" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -4699,10 +4699,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I91" t="n">
         <v>19</v>
@@ -4778,19 +4778,19 @@
         <v>30</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4799,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>30</v>
       </c>
       <c r="B101" t="n">
-        <v>0.4</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -5169,10 +5169,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H101" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>30</v>
       </c>
       <c r="B102" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H102" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
         <v>30</v>
       </c>
       <c r="B108" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5498,10 +5498,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -5530,7 +5530,7 @@
         <v>30</v>
       </c>
       <c r="B109" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -5545,10 +5545,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H109" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
         <v>30</v>
       </c>
       <c r="B114" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -5780,10 +5780,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -5953,7 +5953,7 @@
         <v>30</v>
       </c>
       <c r="B118" t="n">
-        <v>0.8</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -6000,25 +6000,25 @@
         <v>30</v>
       </c>
       <c r="B119" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D119" t="n">
         <v>0.8</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3478260869565218</v>
       </c>
       <c r="F119" t="n">
         <v>4</v>
       </c>
       <c r="G119" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H119" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -6050,25 +6050,25 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="D120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="F120" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" t="n">
+        <v>12</v>
+      </c>
+      <c r="H120" t="n">
+        <v>13</v>
+      </c>
+      <c r="I120" t="n">
         <v>1</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="F120" t="n">
-        <v>5</v>
-      </c>
-      <c r="G120" t="n">
-        <v>11</v>
-      </c>
-      <c r="H120" t="n">
-        <v>14</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6329,25 +6329,25 @@
         <v>30</v>
       </c>
       <c r="B126" t="n">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="D126" t="n">
         <v>0.2</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I126" t="n">
         <v>4</v>
@@ -6376,28 +6376,28 @@
         <v>30</v>
       </c>
       <c r="B127" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="D127" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E127" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G127" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H127" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>30</v>
       </c>
       <c r="B129" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -6485,10 +6485,10 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H129" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I129" t="n">
         <v>20</v>
@@ -6564,7 +6564,7 @@
         <v>30</v>
       </c>
       <c r="B131" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I131" t="n">
         <v>20</v>
@@ -6611,7 +6611,7 @@
         <v>30</v>
       </c>
       <c r="B132" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -6626,10 +6626,10 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I132" t="n">
         <v>20</v>
@@ -6799,7 +6799,7 @@
         <v>30</v>
       </c>
       <c r="B136" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -6814,10 +6814,10 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I136" t="n">
         <v>20</v>
@@ -6849,25 +6849,25 @@
         <v>0.3</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="E137" t="n">
-        <v>0.16</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I137" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6893,25 +6893,25 @@
         <v>30</v>
       </c>
       <c r="B138" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2</v>
       </c>
       <c r="D138" t="n">
         <v>0.1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1481481481481482</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="F138" t="n">
         <v>2</v>
       </c>
       <c r="G138" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H138" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I138" t="n">
         <v>18</v>
@@ -6987,7 +6987,7 @@
         <v>30</v>
       </c>
       <c r="B140" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -7002,10 +7002,10 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I140" t="n">
         <v>20</v>
@@ -7225,25 +7225,25 @@
         <v>0.3</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>0.08695652173913045</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I145" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7350,25 +7350,25 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9056603773584906</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -7397,19 +7397,19 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
@@ -7418,7 +7418,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -7491,19 +7491,19 @@
         <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="D5" t="n">
-        <v>0.875</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.823529411764706</v>
+        <v>0.8679245283018867</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -7538,19 +7538,19 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -7559,7 +7559,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -7682,25 +7682,25 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -7729,25 +7729,25 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8102,19 +8102,19 @@
         <v>30</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>27</v>
@@ -8123,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -8152,25 +8152,25 @@
         <v>0.7</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8352,10 +8352,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -8525,7 +8525,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8540,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
         <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -8587,10 +8587,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8634,10 +8634,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -9042,7 +9042,7 @@
         <v>30</v>
       </c>
       <c r="B38" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -9057,10 +9057,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
         <v>19</v>
@@ -9089,7 +9089,7 @@
         <v>30</v>
       </c>
       <c r="B39" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -9104,10 +9104,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
         <v>19</v>
@@ -9183,7 +9183,7 @@
         <v>30</v>
       </c>
       <c r="B41" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -9198,10 +9198,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
@@ -9371,7 +9371,7 @@
         <v>30</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -9386,10 +9386,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
         <v>19</v>
@@ -9418,7 +9418,7 @@
         <v>30</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -9433,10 +9433,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
         <v>6</v>
-      </c>
-      <c r="H46" t="n">
-        <v>5</v>
       </c>
       <c r="I46" t="n">
         <v>19</v>
@@ -9465,7 +9465,7 @@
         <v>30</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>24</v>
@@ -9512,7 +9512,7 @@
         <v>30</v>
       </c>
       <c r="B48" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -9527,10 +9527,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>24</v>
@@ -9841,7 +9841,7 @@
         <v>30</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9856,10 +9856,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
         <v>24</v>
@@ -9935,7 +9935,7 @@
         <v>30</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -9950,10 +9950,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
         <v>4</v>
-      </c>
-      <c r="H57" t="n">
-        <v>5</v>
       </c>
       <c r="I57" t="n">
         <v>21</v>
@@ -10311,28 +10311,28 @@
         <v>30</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C65" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>23</v>
+      </c>
+      <c r="H65" t="n">
         <v>1</v>
       </c>
-      <c r="D65" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F65" t="n">
-        <v>4</v>
-      </c>
-      <c r="G65" t="n">
-        <v>24</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -10358,19 +10358,19 @@
         <v>30</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E66" t="n">
         <v>0.5</v>
       </c>
-      <c r="E66" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
         <v>24</v>
@@ -10379,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -10640,19 +10640,19 @@
         <v>30</v>
       </c>
       <c r="B72" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>24</v>
@@ -10661,7 +10661,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -10687,19 +10687,19 @@
         <v>30</v>
       </c>
       <c r="B73" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
         <v>23</v>
@@ -10708,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>30</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -10749,10 +10749,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I74" t="n">
         <v>7</v>
@@ -10781,7 +10781,7 @@
         <v>30</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -10796,10 +10796,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H75" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I75" t="n">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>30</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -10937,10 +10937,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I78" t="n">
         <v>7</v>
@@ -11063,7 +11063,7 @@
         <v>30</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -11078,10 +11078,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
+        <v>12</v>
+      </c>
+      <c r="H81" t="n">
         <v>11</v>
-      </c>
-      <c r="H81" t="n">
-        <v>12</v>
       </c>
       <c r="I81" t="n">
         <v>7</v>
@@ -11110,7 +11110,7 @@
         <v>30</v>
       </c>
       <c r="B82" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -11125,10 +11125,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H82" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I82" t="n">
         <v>7</v>
@@ -11204,7 +11204,7 @@
         <v>30</v>
       </c>
       <c r="B84" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -11219,10 +11219,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I84" t="n">
         <v>19</v>
@@ -11345,7 +11345,7 @@
         <v>30</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -11360,10 +11360,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I87" t="n">
         <v>19</v>
@@ -11533,7 +11533,7 @@
         <v>30</v>
       </c>
       <c r="B91" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -11548,10 +11548,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I91" t="n">
         <v>19</v>
@@ -11627,19 +11627,19 @@
         <v>30</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11648,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>30</v>
       </c>
       <c r="B101" t="n">
-        <v>0.4</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -12018,10 +12018,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H101" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -12050,7 +12050,7 @@
         <v>30</v>
       </c>
       <c r="B102" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -12065,10 +12065,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H102" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -12332,7 +12332,7 @@
         <v>30</v>
       </c>
       <c r="B108" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -12347,10 +12347,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         <v>30</v>
       </c>
       <c r="B109" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -12394,10 +12394,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H109" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
         <v>30</v>
       </c>
       <c r="B114" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -12629,10 +12629,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>30</v>
       </c>
       <c r="B118" t="n">
-        <v>0.8</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -12817,10 +12817,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -12849,25 +12849,25 @@
         <v>30</v>
       </c>
       <c r="B119" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="D119" t="n">
         <v>0.8</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3478260869565218</v>
       </c>
       <c r="F119" t="n">
         <v>4</v>
       </c>
       <c r="G119" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H119" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -12899,25 +12899,25 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="D120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="F120" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" t="n">
+        <v>12</v>
+      </c>
+      <c r="H120" t="n">
+        <v>13</v>
+      </c>
+      <c r="I120" t="n">
         <v>1</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="F120" t="n">
-        <v>5</v>
-      </c>
-      <c r="G120" t="n">
-        <v>11</v>
-      </c>
-      <c r="H120" t="n">
-        <v>14</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -13178,25 +13178,25 @@
         <v>30</v>
       </c>
       <c r="B126" t="n">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="D126" t="n">
         <v>0.2</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I126" t="n">
         <v>4</v>
@@ -13225,28 +13225,28 @@
         <v>30</v>
       </c>
       <c r="B127" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="D127" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E127" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G127" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H127" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>30</v>
       </c>
       <c r="B129" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -13334,10 +13334,10 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H129" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I129" t="n">
         <v>20</v>
@@ -13413,7 +13413,7 @@
         <v>30</v>
       </c>
       <c r="B131" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -13428,10 +13428,10 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I131" t="n">
         <v>20</v>
@@ -13460,7 +13460,7 @@
         <v>30</v>
       </c>
       <c r="B132" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -13475,10 +13475,10 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I132" t="n">
         <v>20</v>
@@ -13648,7 +13648,7 @@
         <v>30</v>
       </c>
       <c r="B136" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -13663,10 +13663,10 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I136" t="n">
         <v>20</v>
@@ -13698,25 +13698,25 @@
         <v>0.3</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="E137" t="n">
-        <v>0.16</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I137" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -13742,25 +13742,25 @@
         <v>30</v>
       </c>
       <c r="B138" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2</v>
       </c>
       <c r="D138" t="n">
         <v>0.1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1481481481481482</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="F138" t="n">
         <v>2</v>
       </c>
       <c r="G138" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H138" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I138" t="n">
         <v>18</v>
@@ -13836,7 +13836,7 @@
         <v>30</v>
       </c>
       <c r="B140" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -13851,10 +13851,10 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I140" t="n">
         <v>20</v>
@@ -14074,25 +14074,25 @@
         <v>0.3</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>0.08695652173913045</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I145" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>

--- a/eval/results/evaluation_metrics_by_qid_new30.xlsx
+++ b/eval/results/evaluation_metrics_by_qid_new30.xlsx
@@ -501,25 +501,25 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -548,19 +548,19 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
@@ -569,7 +569,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1347,28 +1347,28 @@
         <v>30</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1394,25 +1394,25 @@
         <v>30</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7666666666666667</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
         <v>23</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1444,19 +1444,19 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1488,25 +1488,25 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1535,28 +1535,28 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1582,25 +1582,25 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
         <v>22</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1629,25 +1629,25 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>20</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1676,28 +1676,28 @@
         <v>30</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1723,25 +1723,25 @@
         <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
         <v>18</v>
       </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1770,28 +1770,28 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.5454545454545455</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1817,19 +1817,19 @@
         <v>30</v>
       </c>
       <c r="B30" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.6250000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>19</v>
@@ -1838,7 +1838,7 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1864,19 +1864,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>23</v>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1911,19 +1911,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>23</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1958,19 +1958,19 @@
         <v>30</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>23</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2005,19 +2005,19 @@
         <v>30</v>
       </c>
       <c r="B34" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>23</v>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2052,19 +2052,19 @@
         <v>30</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>23</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2099,19 +2099,19 @@
         <v>30</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>23</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2146,19 +2146,19 @@
         <v>30</v>
       </c>
       <c r="B37" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
         <v>23</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2193,28 +2193,28 @@
         <v>30</v>
       </c>
       <c r="B38" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2240,28 +2240,28 @@
         <v>30</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
         <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2287,28 +2287,28 @@
         <v>30</v>
       </c>
       <c r="B40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C40" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C40" t="n">
-        <v>0.9375</v>
-      </c>
       <c r="D40" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.625</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F40" t="n">
         <v>15</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2334,28 +2334,28 @@
         <v>30</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
         <v>8</v>
-      </c>
-      <c r="I41" t="n">
-        <v>19</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
         <v>30</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2428,28 +2428,28 @@
         <v>30</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2475,28 +2475,28 @@
         <v>30</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2522,28 +2522,28 @@
         <v>30</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2569,28 +2569,28 @@
         <v>30</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2616,28 +2616,28 @@
         <v>30</v>
       </c>
       <c r="B47" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2663,28 +2663,28 @@
         <v>30</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" t="n">
         <v>3</v>
-      </c>
-      <c r="H48" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" t="n">
-        <v>24</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2710,28 +2710,28 @@
         <v>30</v>
       </c>
       <c r="B49" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="F49" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2757,28 +2757,28 @@
         <v>30</v>
       </c>
       <c r="B50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
         <v>4</v>
-      </c>
-      <c r="I50" t="n">
-        <v>24</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2804,28 +2804,28 @@
         <v>30</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2851,28 +2851,28 @@
         <v>30</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2898,28 +2898,28 @@
         <v>30</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2945,28 +2945,28 @@
         <v>30</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.7647058823529412</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2992,28 +2992,28 @@
         <v>30</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3039,28 +3039,28 @@
         <v>30</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3086,28 +3086,28 @@
         <v>30</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G57" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" t="n">
         <v>5</v>
       </c>
-      <c r="H57" t="n">
-        <v>4</v>
-      </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3133,28 +3133,28 @@
         <v>30</v>
       </c>
       <c r="B58" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8837209302325582</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F58" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3180,28 +3180,28 @@
         <v>30</v>
       </c>
       <c r="B59" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H59" t="n">
         <v>3</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3227,28 +3227,28 @@
         <v>30</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H60" t="n">
         <v>3</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3274,28 +3274,28 @@
         <v>30</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H61" t="n">
         <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3321,28 +3321,28 @@
         <v>30</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H62" t="n">
         <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3368,28 +3368,28 @@
         <v>30</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
         <v>9</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>21</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3415,28 +3415,28 @@
         <v>30</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G64" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" t="n">
         <v>5</v>
       </c>
-      <c r="H64" t="n">
-        <v>4</v>
-      </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3462,28 +3462,28 @@
         <v>30</v>
       </c>
       <c r="B65" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C65" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3509,19 +3509,19 @@
         <v>30</v>
       </c>
       <c r="B66" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>24</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3885,28 +3885,28 @@
         <v>30</v>
       </c>
       <c r="B74" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3932,28 +3932,28 @@
         <v>30</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3979,28 +3979,28 @@
         <v>30</v>
       </c>
       <c r="B76" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7</v>
       </c>
       <c r="E76" t="n">
-        <v>0.923076923076923</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G76" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4026,28 +4026,28 @@
         <v>30</v>
       </c>
       <c r="B77" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>0.846153846153846</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4073,28 +4073,28 @@
         <v>30</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>0.6956521739130436</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4120,28 +4120,28 @@
         <v>30</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>0.846153846153846</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4167,28 +4167,28 @@
         <v>30</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>0.6956521739130436</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4214,28 +4214,28 @@
         <v>30</v>
       </c>
       <c r="B81" t="n">
-        <v>0.4</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>0.5365853658536585</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G81" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4261,28 +4261,28 @@
         <v>30</v>
       </c>
       <c r="B82" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4308,28 +4308,28 @@
         <v>30</v>
       </c>
       <c r="B83" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" t="n">
+        <v>5</v>
+      </c>
+      <c r="I83" t="n">
         <v>9</v>
-      </c>
-      <c r="I83" t="n">
-        <v>19</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4355,28 +4355,28 @@
         <v>30</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G84" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" t="n">
         <v>5</v>
       </c>
-      <c r="H84" t="n">
-        <v>6</v>
-      </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4405,25 +4405,25 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4449,28 +4449,28 @@
         <v>30</v>
       </c>
       <c r="B86" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4496,28 +4496,28 @@
         <v>30</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4543,28 +4543,28 @@
         <v>30</v>
       </c>
       <c r="B88" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G88" t="n">
         <v>8</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4590,28 +4590,28 @@
         <v>30</v>
       </c>
       <c r="B89" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G89" t="n">
         <v>7</v>
       </c>
       <c r="H89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4637,28 +4637,28 @@
         <v>30</v>
       </c>
       <c r="B90" t="n">
-        <v>0.2</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>0.6857142857142856</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4684,28 +4684,28 @@
         <v>30</v>
       </c>
       <c r="B91" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" t="n">
         <v>6</v>
       </c>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4731,28 +4731,28 @@
         <v>30</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I92" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4778,28 +4778,28 @@
         <v>30</v>
       </c>
       <c r="B93" t="n">
-        <v>0.1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4825,28 +4825,28 @@
         <v>30</v>
       </c>
       <c r="B94" t="n">
-        <v>0.7</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="D94" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.744186046511628</v>
       </c>
       <c r="F94" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4872,28 +4872,28 @@
         <v>30</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4919,28 +4919,28 @@
         <v>30</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>0.6842105263157894</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4966,28 +4966,28 @@
         <v>30</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I97" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5013,28 +5013,28 @@
         <v>30</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5060,28 +5060,28 @@
         <v>30</v>
       </c>
       <c r="B99" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="D99" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="E99" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.4375000000000001</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5107,28 +5107,28 @@
         <v>30</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I100" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5154,28 +5154,28 @@
         <v>30</v>
       </c>
       <c r="B101" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G101" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H101" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5201,28 +5201,28 @@
         <v>30</v>
       </c>
       <c r="B102" t="n">
-        <v>0.5</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H102" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5248,28 +5248,28 @@
         <v>30</v>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G103" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5295,28 +5295,28 @@
         <v>30</v>
       </c>
       <c r="B104" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H104" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5342,28 +5342,28 @@
         <v>30</v>
       </c>
       <c r="B105" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G105" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H105" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5389,28 +5389,28 @@
         <v>30</v>
       </c>
       <c r="B106" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G106" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H106" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5436,28 +5436,28 @@
         <v>30</v>
       </c>
       <c r="B107" t="n">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G107" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H107" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5483,28 +5483,28 @@
         <v>30</v>
       </c>
       <c r="B108" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G108" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5530,28 +5530,28 @@
         <v>30</v>
       </c>
       <c r="B109" t="n">
-        <v>0.3</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H109" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5577,25 +5577,25 @@
         <v>30</v>
       </c>
       <c r="B110" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
         <v>22</v>
       </c>
       <c r="H110" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -5624,25 +5624,25 @@
         <v>30</v>
       </c>
       <c r="B111" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G111" t="n">
         <v>22</v>
       </c>
       <c r="H111" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -5671,25 +5671,25 @@
         <v>30</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -5718,25 +5718,25 @@
         <v>30</v>
       </c>
       <c r="B113" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G113" t="n">
         <v>23</v>
       </c>
       <c r="H113" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -5765,25 +5765,25 @@
         <v>30</v>
       </c>
       <c r="B114" t="n">
-        <v>0.8</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G114" t="n">
         <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -5812,25 +5812,25 @@
         <v>30</v>
       </c>
       <c r="B115" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G115" t="n">
         <v>23</v>
       </c>
       <c r="H115" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -5859,25 +5859,25 @@
         <v>30</v>
       </c>
       <c r="B116" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G116" t="n">
         <v>23</v>
       </c>
       <c r="H116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -5906,28 +5906,28 @@
         <v>30</v>
       </c>
       <c r="B117" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5953,25 +5953,25 @@
         <v>30</v>
       </c>
       <c r="B118" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G118" t="n">
         <v>23</v>
       </c>
       <c r="H118" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -6000,25 +6000,25 @@
         <v>30</v>
       </c>
       <c r="B119" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="D119" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3478260869565218</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F119" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G119" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H119" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -6047,28 +6047,28 @@
         <v>30</v>
       </c>
       <c r="B120" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D120" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="F120" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G120" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H120" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6094,28 +6094,28 @@
         <v>30</v>
       </c>
       <c r="B121" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C121" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E121" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.8648648648648648</v>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G121" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6141,28 +6141,28 @@
         <v>30</v>
       </c>
       <c r="B122" t="n">
-        <v>0.4</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D122" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E122" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F122" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G122" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H122" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6188,28 +6188,28 @@
         <v>30</v>
       </c>
       <c r="B123" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1875</v>
+        <v>0.9375</v>
       </c>
       <c r="D123" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G123" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H123" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6235,28 +6235,28 @@
         <v>30</v>
       </c>
       <c r="B124" t="n">
-        <v>0.5</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1875</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H124" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6282,28 +6282,28 @@
         <v>30</v>
       </c>
       <c r="B125" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1875</v>
+        <v>0.8125</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E125" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="F125" t="n">
+        <v>13</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7</v>
+      </c>
+      <c r="H125" t="n">
         <v>3</v>
       </c>
-      <c r="G125" t="n">
-        <v>12</v>
-      </c>
-      <c r="H125" t="n">
-        <v>13</v>
-      </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6329,28 +6329,28 @@
         <v>30</v>
       </c>
       <c r="B126" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E126" t="n">
-        <v>0.125</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G126" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
         <v>10</v>
-      </c>
-      <c r="I126" t="n">
-        <v>4</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6376,25 +6376,25 @@
         <v>30</v>
       </c>
       <c r="B127" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D127" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="E127" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="F127" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G127" t="n">
         <v>7</v>
       </c>
       <c r="H127" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -6423,19 +6423,19 @@
         <v>30</v>
       </c>
       <c r="B128" t="n">
-        <v>0.1</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G128" t="n">
         <v>3</v>
@@ -6444,7 +6444,7 @@
         <v>7</v>
       </c>
       <c r="I128" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6470,28 +6470,28 @@
         <v>30</v>
       </c>
       <c r="B129" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H129" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I129" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6517,19 +6517,19 @@
         <v>30</v>
       </c>
       <c r="B130" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C130" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D130" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8648648648648648</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F130" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G130" t="n">
         <v>9</v>
@@ -6538,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6564,19 +6564,19 @@
         <v>30</v>
       </c>
       <c r="B131" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G131" t="n">
         <v>2</v>
@@ -6585,7 +6585,7 @@
         <v>8</v>
       </c>
       <c r="I131" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6611,19 +6611,19 @@
         <v>30</v>
       </c>
       <c r="B132" t="n">
-        <v>0.1</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G132" t="n">
         <v>3</v>
@@ -6632,7 +6632,7 @@
         <v>7</v>
       </c>
       <c r="I132" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6658,19 +6658,19 @@
         <v>30</v>
       </c>
       <c r="B133" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G133" t="n">
         <v>10</v>
@@ -6679,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6705,19 +6705,19 @@
         <v>30</v>
       </c>
       <c r="B134" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G134" t="n">
         <v>2</v>
@@ -6726,7 +6726,7 @@
         <v>8</v>
       </c>
       <c r="I134" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -6752,19 +6752,19 @@
         <v>30</v>
       </c>
       <c r="B135" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G135" t="n">
         <v>3</v>
@@ -6773,7 +6773,7 @@
         <v>7</v>
       </c>
       <c r="I135" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6799,19 +6799,19 @@
         <v>30</v>
       </c>
       <c r="B136" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G136" t="n">
         <v>8</v>
@@ -6820,7 +6820,7 @@
         <v>2</v>
       </c>
       <c r="I136" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -6846,28 +6846,28 @@
         <v>30</v>
       </c>
       <c r="B137" t="n">
-        <v>0.3</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C137" t="n">
         <v>0.4285714285714285</v>
       </c>
       <c r="D137" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="E137" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H137" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I137" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6893,28 +6893,28 @@
         <v>30</v>
       </c>
       <c r="B138" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="D138" t="n">
-        <v>0.1</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G138" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I138" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -6940,28 +6940,28 @@
         <v>30</v>
       </c>
       <c r="B139" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="C139" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5</v>
       </c>
       <c r="D139" t="n">
-        <v>0.5</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E139" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="F139" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I139" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6987,28 +6987,28 @@
         <v>30</v>
       </c>
       <c r="B140" t="n">
-        <v>0.1</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H140" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I140" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7034,28 +7034,28 @@
         <v>30</v>
       </c>
       <c r="B141" t="n">
-        <v>0.2</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="D141" t="n">
-        <v>0.05</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E141" t="n">
-        <v>0.07692307692307691</v>
+        <v>0.606060606060606</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G141" t="n">
+        <v>7</v>
+      </c>
+      <c r="H141" t="n">
+        <v>8</v>
+      </c>
+      <c r="I141" t="n">
         <v>5</v>
-      </c>
-      <c r="H141" t="n">
-        <v>5</v>
-      </c>
-      <c r="I141" t="n">
-        <v>19</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7081,28 +7081,28 @@
         <v>30</v>
       </c>
       <c r="B142" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -7128,28 +7128,28 @@
         <v>30</v>
       </c>
       <c r="B143" t="n">
-        <v>0.2</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="D143" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="E143" t="n">
-        <v>0.07692307692307691</v>
+        <v>0.6486486486486486</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G143" t="n">
         <v>5</v>
       </c>
       <c r="H143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I143" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -7175,28 +7175,28 @@
         <v>30</v>
       </c>
       <c r="B144" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G144" t="n">
         <v>8</v>
       </c>
       <c r="H144" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I144" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7222,28 +7222,28 @@
         <v>30</v>
       </c>
       <c r="B145" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D145" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D145" t="n">
-        <v>0.05</v>
-      </c>
       <c r="E145" t="n">
-        <v>0.08695652173913045</v>
+        <v>0.4</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H145" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I145" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7350,25 +7350,25 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -7397,19 +7397,19 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
@@ -7418,7 +7418,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -8196,28 +8196,28 @@
         <v>30</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -8243,25 +8243,25 @@
         <v>30</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7666666666666667</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
         <v>23</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -8293,19 +8293,19 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -8337,25 +8337,25 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -8384,28 +8384,28 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -8431,25 +8431,25 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
         <v>22</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -8478,25 +8478,25 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>20</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -8525,28 +8525,28 @@
         <v>30</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -8572,25 +8572,25 @@
         <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
         <v>18</v>
       </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -8619,28 +8619,28 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.5454545454545455</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -8666,19 +8666,19 @@
         <v>30</v>
       </c>
       <c r="B30" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.6250000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>19</v>
@@ -8687,7 +8687,7 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -8713,19 +8713,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>23</v>
@@ -8734,7 +8734,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -8760,19 +8760,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>23</v>
@@ -8781,7 +8781,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8807,19 +8807,19 @@
         <v>30</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>23</v>
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8854,19 +8854,19 @@
         <v>30</v>
       </c>
       <c r="B34" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>23</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8901,19 +8901,19 @@
         <v>30</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>23</v>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8948,19 +8948,19 @@
         <v>30</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>23</v>
@@ -8969,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8995,19 +8995,19 @@
         <v>30</v>
       </c>
       <c r="B37" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
         <v>23</v>
@@ -9016,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -9042,28 +9042,28 @@
         <v>30</v>
       </c>
       <c r="B38" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -9089,28 +9089,28 @@
         <v>30</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
         <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -9136,28 +9136,28 @@
         <v>30</v>
       </c>
       <c r="B40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C40" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C40" t="n">
-        <v>0.9375</v>
-      </c>
       <c r="D40" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.625</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F40" t="n">
         <v>15</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -9183,28 +9183,28 @@
         <v>30</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
         <v>8</v>
-      </c>
-      <c r="I41" t="n">
-        <v>19</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -9230,28 +9230,28 @@
         <v>30</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -9277,28 +9277,28 @@
         <v>30</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -9324,28 +9324,28 @@
         <v>30</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -9371,28 +9371,28 @@
         <v>30</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -9418,28 +9418,28 @@
         <v>30</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -9465,28 +9465,28 @@
         <v>30</v>
       </c>
       <c r="B47" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -9512,28 +9512,28 @@
         <v>30</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" t="n">
         <v>3</v>
-      </c>
-      <c r="H48" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" t="n">
-        <v>24</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -9559,28 +9559,28 @@
         <v>30</v>
       </c>
       <c r="B49" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="F49" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -9606,28 +9606,28 @@
         <v>30</v>
       </c>
       <c r="B50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
         <v>4</v>
-      </c>
-      <c r="I50" t="n">
-        <v>24</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -9653,28 +9653,28 @@
         <v>30</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -9700,28 +9700,28 @@
         <v>30</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -9747,28 +9747,28 @@
         <v>30</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -9794,28 +9794,28 @@
         <v>30</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.7647058823529412</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -9841,28 +9841,28 @@
         <v>30</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -9888,28 +9888,28 @@
         <v>30</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -9935,28 +9935,28 @@
         <v>30</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G57" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" t="n">
         <v>5</v>
       </c>
-      <c r="H57" t="n">
-        <v>4</v>
-      </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -9982,28 +9982,28 @@
         <v>30</v>
       </c>
       <c r="B58" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8837209302325582</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F58" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -10029,28 +10029,28 @@
         <v>30</v>
       </c>
       <c r="B59" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H59" t="n">
         <v>3</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -10076,28 +10076,28 @@
         <v>30</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H60" t="n">
         <v>3</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -10123,28 +10123,28 @@
         <v>30</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H61" t="n">
         <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -10170,28 +10170,28 @@
         <v>30</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H62" t="n">
         <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -10217,28 +10217,28 @@
         <v>30</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
         <v>9</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>21</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -10264,28 +10264,28 @@
         <v>30</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G64" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" t="n">
         <v>5</v>
       </c>
-      <c r="H64" t="n">
-        <v>4</v>
-      </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -10311,28 +10311,28 @@
         <v>30</v>
       </c>
       <c r="B65" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C65" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -10358,19 +10358,19 @@
         <v>30</v>
       </c>
       <c r="B66" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>24</v>
@@ -10379,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -10734,28 +10734,28 @@
         <v>30</v>
       </c>
       <c r="B74" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -10781,28 +10781,28 @@
         <v>30</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -10828,28 +10828,28 @@
         <v>30</v>
       </c>
       <c r="B76" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7</v>
       </c>
       <c r="E76" t="n">
-        <v>0.923076923076923</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G76" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -10875,28 +10875,28 @@
         <v>30</v>
       </c>
       <c r="B77" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>0.846153846153846</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -10922,28 +10922,28 @@
         <v>30</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>0.6956521739130436</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -10969,28 +10969,28 @@
         <v>30</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>0.846153846153846</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -11016,28 +11016,28 @@
         <v>30</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>0.6956521739130436</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -11063,28 +11063,28 @@
         <v>30</v>
       </c>
       <c r="B81" t="n">
-        <v>0.4</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>0.5365853658536585</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G81" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -11110,28 +11110,28 @@
         <v>30</v>
       </c>
       <c r="B82" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -11157,28 +11157,28 @@
         <v>30</v>
       </c>
       <c r="B83" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" t="n">
+        <v>5</v>
+      </c>
+      <c r="I83" t="n">
         <v>9</v>
-      </c>
-      <c r="I83" t="n">
-        <v>19</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -11204,28 +11204,28 @@
         <v>30</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G84" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" t="n">
         <v>5</v>
       </c>
-      <c r="H84" t="n">
-        <v>6</v>
-      </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -11254,25 +11254,25 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -11298,28 +11298,28 @@
         <v>30</v>
       </c>
       <c r="B86" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -11345,28 +11345,28 @@
         <v>30</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -11392,28 +11392,28 @@
         <v>30</v>
       </c>
       <c r="B88" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G88" t="n">
         <v>8</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -11439,28 +11439,28 @@
         <v>30</v>
       </c>
       <c r="B89" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G89" t="n">
         <v>7</v>
       </c>
       <c r="H89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -11486,28 +11486,28 @@
         <v>30</v>
       </c>
       <c r="B90" t="n">
-        <v>0.2</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>0.6857142857142856</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -11533,28 +11533,28 @@
         <v>30</v>
       </c>
       <c r="B91" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" t="n">
         <v>6</v>
       </c>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -11580,28 +11580,28 @@
         <v>30</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I92" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -11627,28 +11627,28 @@
         <v>30</v>
       </c>
       <c r="B93" t="n">
-        <v>0.1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -11674,28 +11674,28 @@
         <v>30</v>
       </c>
       <c r="B94" t="n">
-        <v>0.7</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="D94" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.744186046511628</v>
       </c>
       <c r="F94" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -11721,28 +11721,28 @@
         <v>30</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -11768,28 +11768,28 @@
         <v>30</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>0.6842105263157894</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -11815,28 +11815,28 @@
         <v>30</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I97" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -11862,28 +11862,28 @@
         <v>30</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -11909,28 +11909,28 @@
         <v>30</v>
       </c>
       <c r="B99" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="D99" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="E99" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.4375000000000001</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -11956,28 +11956,28 @@
         <v>30</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I100" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -12003,28 +12003,28 @@
         <v>30</v>
       </c>
       <c r="B101" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G101" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H101" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -12050,28 +12050,28 @@
         <v>30</v>
       </c>
       <c r="B102" t="n">
-        <v>0.5</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H102" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -12097,28 +12097,28 @@
         <v>30</v>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G103" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -12144,28 +12144,28 @@
         <v>30</v>
       </c>
       <c r="B104" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H104" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -12191,28 +12191,28 @@
         <v>30</v>
       </c>
       <c r="B105" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G105" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H105" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -12238,28 +12238,28 @@
         <v>30</v>
       </c>
       <c r="B106" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G106" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H106" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -12285,28 +12285,28 @@
         <v>30</v>
       </c>
       <c r="B107" t="n">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G107" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H107" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -12332,28 +12332,28 @@
         <v>30</v>
       </c>
       <c r="B108" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G108" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -12379,28 +12379,28 @@
         <v>30</v>
       </c>
       <c r="B109" t="n">
-        <v>0.3</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H109" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -12426,25 +12426,25 @@
         <v>30</v>
       </c>
       <c r="B110" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
         <v>22</v>
       </c>
       <c r="H110" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -12473,25 +12473,25 @@
         <v>30</v>
       </c>
       <c r="B111" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G111" t="n">
         <v>22</v>
       </c>
       <c r="H111" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -12520,25 +12520,25 @@
         <v>30</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -12567,25 +12567,25 @@
         <v>30</v>
       </c>
       <c r="B113" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G113" t="n">
         <v>23</v>
       </c>
       <c r="H113" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -12614,25 +12614,25 @@
         <v>30</v>
       </c>
       <c r="B114" t="n">
-        <v>0.8</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G114" t="n">
         <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -12661,25 +12661,25 @@
         <v>30</v>
       </c>
       <c r="B115" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G115" t="n">
         <v>23</v>
       </c>
       <c r="H115" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -12708,25 +12708,25 @@
         <v>30</v>
       </c>
       <c r="B116" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G116" t="n">
         <v>23</v>
       </c>
       <c r="H116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -12755,28 +12755,28 @@
         <v>30</v>
       </c>
       <c r="B117" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -12802,25 +12802,25 @@
         <v>30</v>
       </c>
       <c r="B118" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G118" t="n">
         <v>23</v>
       </c>
       <c r="H118" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -12849,25 +12849,25 @@
         <v>30</v>
       </c>
       <c r="B119" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="D119" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3478260869565218</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F119" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G119" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H119" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -12896,28 +12896,28 @@
         <v>30</v>
       </c>
       <c r="B120" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D120" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="F120" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G120" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H120" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -12943,28 +12943,28 @@
         <v>30</v>
       </c>
       <c r="B121" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C121" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E121" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.8648648648648648</v>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G121" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -12990,28 +12990,28 @@
         <v>30</v>
       </c>
       <c r="B122" t="n">
-        <v>0.4</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D122" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E122" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F122" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G122" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H122" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -13037,28 +13037,28 @@
         <v>30</v>
       </c>
       <c r="B123" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1875</v>
+        <v>0.9375</v>
       </c>
       <c r="D123" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G123" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H123" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -13084,28 +13084,28 @@
         <v>30</v>
       </c>
       <c r="B124" t="n">
-        <v>0.5</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1875</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G124" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H124" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -13131,28 +13131,28 @@
         <v>30</v>
       </c>
       <c r="B125" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1875</v>
+        <v>0.8125</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E125" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="F125" t="n">
+        <v>13</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7</v>
+      </c>
+      <c r="H125" t="n">
         <v>3</v>
       </c>
-      <c r="G125" t="n">
-        <v>12</v>
-      </c>
-      <c r="H125" t="n">
-        <v>13</v>
-      </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -13178,28 +13178,28 @@
         <v>30</v>
       </c>
       <c r="B126" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E126" t="n">
-        <v>0.125</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G126" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
         <v>10</v>
-      </c>
-      <c r="I126" t="n">
-        <v>4</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -13225,25 +13225,25 @@
         <v>30</v>
       </c>
       <c r="B127" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D127" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="E127" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="F127" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G127" t="n">
         <v>7</v>
       </c>
       <c r="H127" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -13272,19 +13272,19 @@
         <v>30</v>
       </c>
       <c r="B128" t="n">
-        <v>0.1</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G128" t="n">
         <v>3</v>
@@ -13293,7 +13293,7 @@
         <v>7</v>
       </c>
       <c r="I128" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -13319,28 +13319,28 @@
         <v>30</v>
       </c>
       <c r="B129" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H129" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I129" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -13366,19 +13366,19 @@
         <v>30</v>
       </c>
       <c r="B130" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C130" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D130" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8648648648648648</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F130" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G130" t="n">
         <v>9</v>
@@ -13387,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -13413,19 +13413,19 @@
         <v>30</v>
       </c>
       <c r="B131" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G131" t="n">
         <v>2</v>
@@ -13434,7 +13434,7 @@
         <v>8</v>
       </c>
       <c r="I131" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -13460,19 +13460,19 @@
         <v>30</v>
       </c>
       <c r="B132" t="n">
-        <v>0.1</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G132" t="n">
         <v>3</v>
@@ -13481,7 +13481,7 @@
         <v>7</v>
       </c>
       <c r="I132" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -13507,19 +13507,19 @@
         <v>30</v>
       </c>
       <c r="B133" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G133" t="n">
         <v>10</v>
@@ -13528,7 +13528,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -13554,19 +13554,19 @@
         <v>30</v>
       </c>
       <c r="B134" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G134" t="n">
         <v>2</v>
@@ -13575,7 +13575,7 @@
         <v>8</v>
       </c>
       <c r="I134" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -13601,19 +13601,19 @@
         <v>30</v>
       </c>
       <c r="B135" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G135" t="n">
         <v>3</v>
@@ -13622,7 +13622,7 @@
         <v>7</v>
       </c>
       <c r="I135" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -13648,19 +13648,19 @@
         <v>30</v>
       </c>
       <c r="B136" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G136" t="n">
         <v>8</v>
@@ -13669,7 +13669,7 @@
         <v>2</v>
       </c>
       <c r="I136" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -13695,28 +13695,28 @@
         <v>30</v>
       </c>
       <c r="B137" t="n">
-        <v>0.3</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C137" t="n">
         <v>0.4285714285714285</v>
       </c>
       <c r="D137" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="E137" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H137" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I137" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -13742,28 +13742,28 @@
         <v>30</v>
       </c>
       <c r="B138" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="D138" t="n">
-        <v>0.1</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G138" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I138" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -13789,28 +13789,28 @@
         <v>30</v>
       </c>
       <c r="B139" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="C139" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5</v>
       </c>
       <c r="D139" t="n">
-        <v>0.5</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E139" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="F139" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I139" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -13836,28 +13836,28 @@
         <v>30</v>
       </c>
       <c r="B140" t="n">
-        <v>0.1</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H140" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I140" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -13883,28 +13883,28 @@
         <v>30</v>
       </c>
       <c r="B141" t="n">
-        <v>0.2</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="D141" t="n">
-        <v>0.05</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E141" t="n">
-        <v>0.07692307692307691</v>
+        <v>0.606060606060606</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G141" t="n">
+        <v>7</v>
+      </c>
+      <c r="H141" t="n">
+        <v>8</v>
+      </c>
+      <c r="I141" t="n">
         <v>5</v>
-      </c>
-      <c r="H141" t="n">
-        <v>5</v>
-      </c>
-      <c r="I141" t="n">
-        <v>19</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -13930,28 +13930,28 @@
         <v>30</v>
       </c>
       <c r="B142" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G142" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -13977,28 +13977,28 @@
         <v>30</v>
       </c>
       <c r="B143" t="n">
-        <v>0.2</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="D143" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="E143" t="n">
-        <v>0.07692307692307691</v>
+        <v>0.6486486486486486</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G143" t="n">
         <v>5</v>
       </c>
       <c r="H143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I143" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -14024,28 +14024,28 @@
         <v>30</v>
       </c>
       <c r="B144" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G144" t="n">
         <v>8</v>
       </c>
       <c r="H144" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I144" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -14071,28 +14071,28 @@
         <v>30</v>
       </c>
       <c r="B145" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D145" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D145" t="n">
-        <v>0.05</v>
-      </c>
       <c r="E145" t="n">
-        <v>0.08695652173913045</v>
+        <v>0.4</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H145" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I145" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
